--- a/data/trans_dic/P55$pareja-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,53; 86,02</t>
+          <t>18,03; 88,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,98</t>
+          <t>0,0; 82,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 90,5</t>
+          <t>26,16; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,37; 62,42</t>
+          <t>19,05; 63,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 52,75</t>
+          <t>6,41; 55,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,22</t>
+          <t>0,0; 71,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 33,62</t>
+          <t>3,43; 33,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,95; 55,93</t>
+          <t>15,72; 55,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,23</t>
+          <t>0,0; 69,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,31; 72,18</t>
+          <t>17,38; 69,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,11; 41,23</t>
+          <t>14,02; 41,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,4; 88,73</t>
+          <t>20,69; 83,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,31; 90,73</t>
+          <t>13,87; 89,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,33; 73,78</t>
+          <t>15,21; 71,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,57; 49,6</t>
+          <t>13,58; 51,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,73</t>
+          <t>0,0; 62,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 34,83</t>
+          <t>4,55; 34,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,33; 60,77</t>
+          <t>14,33; 58,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,25; 69,34</t>
+          <t>17,06; 67,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,21; 47,26</t>
+          <t>9,27; 48,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 38,75</t>
+          <t>13,2; 38,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,33; 68,46</t>
+          <t>24,0; 67,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,02; 63,39</t>
+          <t>18,42; 63,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 52,66</t>
+          <t>13,19; 52,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,49; 56,98</t>
+          <t>23,8; 57,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 44,62</t>
+          <t>5,34; 48,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,87</t>
+          <t>0,0; 33,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 33,38</t>
+          <t>9,56; 33,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,14; 51,21</t>
+          <t>16,76; 51,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,84; 49,42</t>
+          <t>18,68; 48,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 34,58</t>
+          <t>7,68; 32,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,88; 41,67</t>
+          <t>19,34; 40,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,47; 60,32</t>
+          <t>37,45; 59,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,98; 54,25</t>
+          <t>27,2; 53,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,93; 60,39</t>
+          <t>32,76; 61,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,14; 42,25</t>
+          <t>23,98; 41,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 27,3</t>
+          <t>3,52; 31,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 39,65</t>
+          <t>4,52; 39,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,75; 51,54</t>
+          <t>13,69; 49,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,86; 28,41</t>
+          <t>11,29; 28,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,26; 48,91</t>
+          <t>29,01; 48,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,63; 45,15</t>
+          <t>24,11; 45,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,34; 50,79</t>
+          <t>28,03; 49,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,43; 34,52</t>
+          <t>21,23; 34,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,96; 75,88</t>
+          <t>28,9; 76,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,46; 52,57</t>
+          <t>20,39; 52,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,58; 58,73</t>
+          <t>31,79; 58,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,64; 57,31</t>
+          <t>29,58; 55,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 31,31</t>
+          <t>6,13; 31,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 24,46</t>
+          <t>8,53; 23,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 28,49</t>
+          <t>7,67; 27,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,75; 16,27</t>
+          <t>7,09; 16,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,87; 40,18</t>
+          <t>16,27; 39,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,08; 28,78</t>
+          <t>13,98; 28,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,59; 40,84</t>
+          <t>21,51; 40,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,24; 24,76</t>
+          <t>14,14; 24,28</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 15,31</t>
+          <t>5,5; 15,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 22,48</t>
+          <t>9,85; 22,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 24,38</t>
+          <t>11,03; 24,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,27</t>
+          <t>6,36; 13,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,16; 15,03</t>
+          <t>5,6; 15,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,7; 22,48</t>
+          <t>9,85; 22,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 24,38</t>
+          <t>11,03; 24,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,36</t>
+          <t>6,26; 13,68</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,63; 56,61</t>
+          <t>40,84; 57,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,16; 49,13</t>
+          <t>30,49; 47,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,42; 52,5</t>
+          <t>35,67; 53,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,99; 41,53</t>
+          <t>29,49; 41,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,62</t>
+          <t>7,21; 15,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 20,3</t>
+          <t>11,69; 20,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,03; 23,17</t>
+          <t>13,09; 23,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,2</t>
+          <t>9,93; 15,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,12; 28,97</t>
+          <t>19,7; 29,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,96; 29,02</t>
+          <t>19,58; 28,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,68; 31,04</t>
+          <t>21,46; 30,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,02; 22,69</t>
+          <t>17,15; 22,71</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1778; 8726</t>
+          <t>1828; 9019</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6634</t>
+          <t>0; 6942</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>975; 6360</t>
+          <t>1838; 7028</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2204; 7488</t>
+          <t>2285; 7603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>847; 7052</t>
+          <t>857; 7352</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5167</t>
+          <t>0; 5719</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>488; 4659</t>
+          <t>475; 4608</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3751; 13149</t>
+          <t>3696; 12932</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7957</t>
+          <t>0; 8060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2610; 10880</t>
+          <t>2620; 10420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3907; 10660</t>
+          <t>3624; 10701</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2311; 9581</t>
+          <t>2234; 9017</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2312; 8628</t>
+          <t>1319; 8522</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1648; 7935</t>
+          <t>1636; 7738</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2370; 8659</t>
+          <t>2371; 8977</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1636</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5437</t>
+          <t>0; 5516</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1773</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>784; 4778</t>
+          <t>624; 4800</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2314; 9814</t>
+          <t>2315; 9406</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3342; 12701</t>
+          <t>3125; 12289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1608; 8254</t>
+          <t>1620; 8403</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4247; 12079</t>
+          <t>4116; 11945</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4564; 12336</t>
+          <t>4325; 12210</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4648; 15489</t>
+          <t>4500; 15482</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1767; 8680</t>
+          <t>2174; 8693</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5189; 12072</t>
+          <t>5043; 12251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1726</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>997; 8479</t>
+          <t>1014; 9297</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4380</t>
+          <t>0; 5464</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1792; 7070</t>
+          <t>2025; 7032</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4250; 13487</t>
+          <t>4414; 13522</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7748; 21466</t>
+          <t>8116; 21187</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2512; 11337</t>
+          <t>2517; 10581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8846; 17652</t>
+          <t>8193; 17311</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25761; 42604</t>
+          <t>26448; 41736</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18286; 36775</t>
+          <t>18442; 36436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12730; 24073</t>
+          <t>13058; 24439</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17388; 30432</t>
+          <t>17273; 30239</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>833; 6395</t>
+          <t>825; 7311</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65; 8262</t>
+          <t>942; 8264</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4187; 16918</t>
+          <t>4494; 16310</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4601; 11020</t>
+          <t>4380; 11187</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27518; 45997</t>
+          <t>27284; 45649</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20944; 40019</t>
+          <t>21366; 40337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19872; 36918</t>
+          <t>20374; 36182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23745; 38253</t>
+          <t>23522; 38125</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4656; 12201</t>
+          <t>4647; 12258</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7374; 18943</t>
+          <t>7345; 18861</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14947; 27796</t>
+          <t>15047; 27544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8912; 17229</t>
+          <t>8893; 16834</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2035; 11400</t>
+          <t>2232; 11633</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7031; 20442</t>
+          <t>7126; 20007</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3830; 15108</t>
+          <t>4066; 14565</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7226; 15167</t>
+          <t>6606; 15741</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8330; 21090</t>
+          <t>8540; 20872</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16841; 34421</t>
+          <t>16724; 34507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21664; 40980</t>
+          <t>21584; 40162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17556; 30523</t>
+          <t>17431; 29933</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 705</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7768; 22049</t>
+          <t>7929; 22434</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13885; 32175</t>
+          <t>14101; 31541</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15612; 35897</t>
+          <t>16244; 35739</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9047; 18704</t>
+          <t>8973; 19232</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7479; 21781</t>
+          <t>8117; 21800</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13885; 32175</t>
+          <t>14101; 31541</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15612; 35897</t>
+          <t>16244; 35739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8875; 19126</t>
+          <t>8956; 19586</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>51428; 71659</t>
+          <t>51690; 72241</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45551; 71809</t>
+          <t>44567; 69964</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43026; 63764</t>
+          <t>43323; 64488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44903; 64331</t>
+          <t>45681; 64151</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16804; 36065</t>
+          <t>16649; 34700</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30598; 56534</t>
+          <t>32555; 57515</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34412; 61205</t>
+          <t>34592; 61049</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31782; 48907</t>
+          <t>31964; 48335</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>71914; 103582</t>
+          <t>70432; 104258</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84796; 123267</t>
+          <t>83173; 119087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83621; 119698</t>
+          <t>82747; 117918</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>81118; 108133</t>
+          <t>81763; 108240</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$pareja-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,03; 88,9</t>
+          <t>16,91; 81,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,65</t>
+          <t>0,0; 82,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,16; 100,0</t>
+          <t>20,82; 89,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 63,38</t>
+          <t>21,18; 66,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 55,0</t>
+          <t>6,43; 53,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,09</t>
+          <t>0,0; 70,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 33,25</t>
+          <t>4,22; 33,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,72; 55,0</t>
+          <t>15,74; 56,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,12</t>
+          <t>0,0; 66,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,38; 69,13</t>
+          <t>17,69; 68,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,02; 41,39</t>
+          <t>15,85; 42,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,69; 83,51</t>
+          <t>21,87; 88,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,87; 89,62</t>
+          <t>24,16; 90,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,21; 71,96</t>
+          <t>15,34; 73,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,58; 51,42</t>
+          <t>16,54; 55,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,63</t>
+          <t>0,0; 62,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 34,99</t>
+          <t>6,91; 37,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,33; 58,24</t>
+          <t>14,78; 62,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 67,09</t>
+          <t>17,58; 70,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 48,11</t>
+          <t>9,51; 50,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,2; 38,31</t>
+          <t>14,8; 39,52</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,0; 67,77</t>
+          <t>25,77; 69,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,42; 63,36</t>
+          <t>18,19; 62,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 52,74</t>
+          <t>11,13; 54,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,8; 57,82</t>
+          <t>24,53; 58,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 48,93</t>
+          <t>6,34; 49,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,52</t>
+          <t>0,0; 32,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,56; 33,2</t>
+          <t>9,41; 35,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 51,34</t>
+          <t>16,14; 50,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 48,77</t>
+          <t>16,49; 48,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,68; 32,28</t>
+          <t>7,87; 35,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,34; 40,86</t>
+          <t>20,47; 41,09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,45; 59,09</t>
+          <t>37,82; 60,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,2; 53,75</t>
+          <t>27,51; 52,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,76; 61,31</t>
+          <t>31,53; 60,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,98; 41,98</t>
+          <t>25,03; 41,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 31,22</t>
+          <t>3,49; 27,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 39,66</t>
+          <t>4,79; 39,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 49,69</t>
+          <t>14,0; 52,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 28,84</t>
+          <t>12,87; 31,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,01; 48,54</t>
+          <t>30,6; 48,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,11; 45,51</t>
+          <t>24,28; 46,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,03; 49,78</t>
+          <t>27,51; 50,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 34,4</t>
+          <t>21,3; 34,73</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,9; 76,23</t>
+          <t>29,08; 76,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,39; 52,34</t>
+          <t>20,31; 52,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,79; 58,2</t>
+          <t>31,63; 58,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,58; 55,99</t>
+          <t>29,8; 58,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 31,95</t>
+          <t>5,98; 31,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 23,94</t>
+          <t>8,46; 24,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 27,47</t>
+          <t>7,91; 31,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,09; 16,89</t>
+          <t>7,46; 17,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,27; 39,76</t>
+          <t>17,05; 41,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 28,85</t>
+          <t>13,84; 28,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,51; 40,02</t>
+          <t>21,07; 39,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,14; 24,28</t>
+          <t>14,66; 25,49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,5; 15,57</t>
+          <t>5,76; 15,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 22,04</t>
+          <t>9,14; 21,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 24,27</t>
+          <t>10,78; 25,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,64</t>
+          <t>6,25; 13,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,6; 15,04</t>
+          <t>5,43; 14,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 22,04</t>
+          <t>9,14; 21,95</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 24,27</t>
+          <t>10,78; 25,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,26; 13,68</t>
+          <t>6,13; 13,07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,84; 57,07</t>
+          <t>39,28; 58,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,49; 47,87</t>
+          <t>30,9; 49,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,67; 53,09</t>
+          <t>36,68; 53,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,49; 41,42</t>
+          <t>29,54; 41,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,03</t>
+          <t>7,31; 15,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,69; 20,65</t>
+          <t>11,24; 20,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,09; 23,11</t>
+          <t>12,54; 22,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 15,02</t>
+          <t>10,23; 15,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,7; 29,16</t>
+          <t>19,94; 28,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,58; 28,04</t>
+          <t>19,97; 28,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,46; 30,58</t>
+          <t>21,62; 30,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,15; 22,71</t>
+          <t>17,51; 22,85</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>7440</t>
         </is>
       </c>
     </row>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1828; 9019</t>
+          <t>1716; 8253</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6942</t>
+          <t>0; 6928</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1838; 7028</t>
+          <t>1463; 6324</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2285; 7603</t>
+          <t>2647; 8370</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>857; 7352</t>
+          <t>859; 7164</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5719</t>
+          <t>0; 5696</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>475; 4608</t>
+          <t>633; 5034</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3696; 12932</t>
+          <t>3701; 13254</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 8060</t>
+          <t>0; 7784</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2620; 10420</t>
+          <t>2667; 10367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3624; 10701</t>
+          <t>4356; 11699</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>9030</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2234; 9017</t>
+          <t>2361; 9524</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1319; 8522</t>
+          <t>2297; 8648</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1636; 7738</t>
+          <t>1650; 7927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2371; 8977</t>
+          <t>3102; 10366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5516</t>
+          <t>0; 5530</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>624; 4800</t>
+          <t>1073; 5764</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2315; 9406</t>
+          <t>2387; 10068</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3125; 12289</t>
+          <t>3220; 12890</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1620; 8403</t>
+          <t>1661; 8860</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4116; 11945</t>
+          <t>5075; 13552</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12496</t>
+          <t>14060</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4325; 12210</t>
+          <t>4643; 12561</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4500; 15482</t>
+          <t>4444; 15176</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2174; 8693</t>
+          <t>1834; 9014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5043; 12251</t>
+          <t>5589; 13320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,37 +2368,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1014; 9297</t>
+          <t>1205; 9471</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5464</t>
+          <t>0; 5216</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2025; 7032</t>
+          <t>2247; 8375</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4414; 13522</t>
+          <t>4250; 13294</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8116; 21187</t>
+          <t>7165; 20883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2517; 10581</t>
+          <t>2579; 11526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8193; 17311</t>
+          <t>9552; 19176</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30741</t>
+          <t>33109</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26448; 41736</t>
+          <t>26712; 42643</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18442; 36436</t>
+          <t>18652; 35810</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13058; 24439</t>
+          <t>12567; 24201</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17273; 30239</t>
+          <t>19307; 32370</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>825; 7311</t>
+          <t>817; 6343</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>942; 8264</t>
+          <t>998; 8244</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4494; 16310</t>
+          <t>4594; 17079</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4380; 11187</t>
+          <t>5384; 13012</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27284; 45649</t>
+          <t>28774; 46015</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21366; 40337</t>
+          <t>21516; 41321</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20374; 36182</t>
+          <t>19998; 36580</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23522; 38125</t>
+          <t>25339; 41315</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>25953</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4647; 12258</t>
+          <t>4675; 12292</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7345; 18861</t>
+          <t>7319; 18825</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15047; 27544</t>
+          <t>14972; 27881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8893; 16834</t>
+          <t>9798; 19127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2232; 11633</t>
+          <t>2178; 11591</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7126; 20007</t>
+          <t>7069; 20441</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4066; 14565</t>
+          <t>4192; 16546</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6606; 15741</t>
+          <t>7517; 17433</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8540; 20872</t>
+          <t>8949; 22012</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16724; 34507</t>
+          <t>16550; 34486</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21584; 40162</t>
+          <t>21145; 40073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17431; 29933</t>
+          <t>19591; 34064</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>14283</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7929; 22434</t>
+          <t>8292; 21885</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14101; 31541</t>
+          <t>13076; 31407</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16244; 35739</t>
+          <t>15882; 37832</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8973; 19232</t>
+          <t>9501; 19965</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8117; 21800</t>
+          <t>7865; 21610</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14101; 31541</t>
+          <t>13076; 31407</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16244; 35739</t>
+          <t>15882; 37832</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8956; 19586</t>
+          <t>9463; 20159</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54689</t>
+          <t>59690</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94163</t>
+          <t>103875</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>51690; 72241</t>
+          <t>49719; 73993</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44567; 69964</t>
+          <t>45161; 71663</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43323; 64488</t>
+          <t>44557; 64999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45681; 64151</t>
+          <t>49111; 69309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16649; 34700</t>
+          <t>16892; 35436</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32555; 57515</t>
+          <t>31318; 56212</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34592; 61049</t>
+          <t>33131; 60554</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31964; 48335</t>
+          <t>35698; 52878</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>70432; 104258</t>
+          <t>71300; 103352</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>83173; 119087</t>
+          <t>84815; 121666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82747; 117918</t>
+          <t>83383; 118742</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>81763; 108240</t>
+          <t>90222; 117755</t>
         </is>
       </c>
     </row>
